--- a/diseases/d071/2010-2014.xlsx
+++ b/diseases/d071/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36248,7 +36248,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">

--- a/diseases/d071/2010-2014.xlsx
+++ b/diseases/d071/2010-2014.xlsx
@@ -769,11 +769,11 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2754591604921949</v>
+        <v>0.2776472693916818</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -1561,11 +1561,11 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2696140695228467</v>
+        <v>0.2717557479622048</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1957,11 +1957,11 @@
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3640973754450957</v>
+        <v>0.3669895817019785</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -2749,11 +2749,11 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3423447584199264</v>
+        <v>0.3450641728378489</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -3541,11 +3541,11 @@
         <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3461181715773538</v>
+        <v>0.3488675600897898</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -4333,11 +4333,11 @@
         <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3223678652335465</v>
+        <v>0.3249285932687503</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -5125,11 +5125,11 @@
         <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3210360723544545</v>
+        <v>0.3235862212974771</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -5917,11 +5917,11 @@
         <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3256973474312764</v>
+        <v>0.3282845231969334</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -6709,11 +6709,11 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3075701665769687</v>
+        <v>0.3100133491434921</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7501,11 +7501,11 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0.3075701665769687</v>
+        <v>0.3100133491434921</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -7897,11 +7897,11 @@
         <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>0.31733664769031</v>
+        <v>0.3198574102661625</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -8689,11 +8689,11 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.2908487670950358</v>
+        <v>0.2931591232819503</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -9085,11 +9085,11 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.278478084875069</v>
+        <v>0.2807672922410982</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -9877,11 +9877,11 @@
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>0.260172635262109</v>
+        <v>0.2623113641080376</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -10669,11 +10669,11 @@
         <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>0.3683144681161815</v>
+        <v>0.3713421684603753</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -11461,11 +11461,11 @@
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.3467743205796464</v>
+        <v>0.3496249518218744</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -12253,11 +12253,11 @@
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0.3284688709666864</v>
+        <v>0.3311690236888138</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -13045,11 +13045,11 @@
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.3086195882538383</v>
+        <v>0.3111565714963385</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -13837,11 +13837,11 @@
         <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>0.3145743730676928</v>
+        <v>0.3171603071540811</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -14233,11 +14233,11 @@
         <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>0.3207497054672455</v>
+        <v>0.3233864033917401</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -15025,11 +15025,11 @@
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3091341992871344</v>
+        <v>0.3116754128494767</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -15817,11 +15817,11 @@
         <v>2</v>
       </c>
       <c r="R78" t="n">
-        <v>0.2901671069170795</v>
+        <v>0.292552402976667</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -16609,11 +16609,11 @@
         <v>4</v>
       </c>
       <c r="R82" t="n">
-        <v>0.2976657248308222</v>
+        <v>0.3001126626938243</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -17005,11 +17005,11 @@
         <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>0.2760520614323875</v>
+        <v>0.2783213258620179</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -17401,11 +17401,11 @@
         <v>3</v>
       </c>
       <c r="R86" t="n">
-        <v>0.2365790901026466</v>
+        <v>0.2383720074748753</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -18193,11 +18193,11 @@
         <v>4</v>
       </c>
       <c r="R90" t="n">
-        <v>0.3003240116025264</v>
+        <v>0.30260002060005</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -18985,11 +18985,11 @@
         <v>3</v>
       </c>
       <c r="R94" t="n">
-        <v>0.3280709419232072</v>
+        <v>0.3305572313532761</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -19777,11 +19777,11 @@
         <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>0.2974763003327723</v>
+        <v>0.2997307279174821</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -20173,11 +20173,11 @@
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.2967461179559123</v>
+        <v>0.2989950118450287</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -20569,11 +20569,11 @@
         <v>2</v>
       </c>
       <c r="R102" t="n">
-        <v>0.2782725038213538</v>
+        <v>0.2803813952119598</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -21361,11 +21361,11 @@
         <v>1</v>
       </c>
       <c r="R106" t="n">
-        <v>0.285063199926152</v>
+        <v>0.2872235546857757</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -22153,11 +22153,11 @@
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.2926570966454962</v>
+        <v>0.2948750018392902</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -22945,11 +22945,11 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0.2595798349737373</v>
+        <v>0.2615470637571549</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -23341,11 +23341,11 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0.2614783091535733</v>
+        <v>0.2634599255455334</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -24133,11 +24133,11 @@
         <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>0.250890664689103</v>
+        <v>0.2527920424949603</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -24529,11 +24529,11 @@
         <v>6</v>
       </c>
       <c r="R122" t="n">
-        <v>0.2376743636679367</v>
+        <v>0.2394755815835553</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -25321,11 +25321,11 @@
         <v>2</v>
       </c>
       <c r="R126" t="n">
-        <v>0.2435808857780188</v>
+        <v>0.2456738294106461</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -25717,11 +25717,11 @@
         <v>1</v>
       </c>
       <c r="R128" t="n">
-        <v>0.2137043377159337</v>
+        <v>0.2155405701914778</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -26113,11 +26113,11 @@
         <v>3</v>
       </c>
       <c r="R130" t="n">
-        <v>0.2720796318663669</v>
+        <v>0.2744174480347557</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -26509,11 +26509,11 @@
         <v>1</v>
       </c>
       <c r="R132" t="n">
-        <v>0.2474967440191659</v>
+        <v>0.2496233342597604</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -27301,11 +27301,11 @@
         <v>4</v>
       </c>
       <c r="R136" t="n">
-        <v>0.2477142916992296</v>
+        <v>0.2498427511958223</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -28093,11 +28093,11 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>0.2292227388938128</v>
+        <v>0.2311923116305604</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -28885,11 +28885,11 @@
         <v>1</v>
       </c>
       <c r="R144" t="n">
-        <v>0.2498897684998668</v>
+        <v>0.2520369205564414</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -29281,11 +29281,11 @@
         <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>0.2530804678074681</v>
+        <v>0.2552550356186826</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -29677,11 +29677,11 @@
         <v>1</v>
       </c>
       <c r="R148" t="n">
-        <v>0.2498897684998668</v>
+        <v>0.2520369205564414</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
@@ -30469,11 +30469,11 @@
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>0.2270472620931756</v>
+        <v>0.2289981422699414</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -31261,11 +31261,11 @@
         <v>4</v>
       </c>
       <c r="R156" t="n">
-        <v>0.2246542376124746</v>
+        <v>0.2265845559732604</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -32053,11 +32053,11 @@
         <v>1</v>
       </c>
       <c r="R160" t="n">
-        <v>0.2090633205412409</v>
+        <v>0.2108596755554905</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U160" t="inlineStr">
@@ -32449,11 +32449,11 @@
         <v>1</v>
       </c>
       <c r="R162" t="n">
-        <v>0.2190998003783952</v>
+        <v>0.2209290498815803</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
@@ -32845,11 +32845,11 @@
         <v>1</v>
       </c>
       <c r="R164" t="n">
-        <v>0.2052664686872897</v>
+        <v>0.2069802246342066</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U164" t="inlineStr">
@@ -33241,11 +33241,11 @@
         <v>4</v>
       </c>
       <c r="R166" t="n">
-        <v>0.2304834795825341</v>
+        <v>0.2324077706580649</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
@@ -33637,11 +33637,11 @@
         <v>1</v>
       </c>
       <c r="R168" t="n">
-        <v>0.2237829595446549</v>
+        <v>0.2256513084288683</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U168" t="inlineStr">
@@ -34033,11 +34033,11 @@
         <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>0.2106701138791278</v>
+        <v>0.2124289844964619</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U170" t="inlineStr">
@@ -34429,11 +34429,11 @@
         <v>1</v>
       </c>
       <c r="R172" t="n">
-        <v>0.2055546630975211</v>
+        <v>0.2072708251601935</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
@@ -34825,11 +34825,11 @@
         <v>2</v>
       </c>
       <c r="R174" t="n">
-        <v>0.2170824395067757</v>
+        <v>0.2188948461996716</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U174" t="inlineStr">
@@ -35221,11 +35221,11 @@
         <v>2</v>
       </c>
       <c r="R176" t="n">
-        <v>0.2190998003783952</v>
+        <v>0.2209290498815803</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U176" t="inlineStr">
@@ -36013,11 +36013,11 @@
         <v>1</v>
       </c>
       <c r="R180" t="n">
-        <v>0.2048341770719427</v>
+        <v>0.2065443238452261</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U180" t="inlineStr">
@@ -36409,11 +36409,11 @@
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>0.1996466776877781</v>
+        <v>0.201313514377461</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
@@ -36805,11 +36805,11 @@
         <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>0.1826432074841275</v>
+        <v>0.1841680833442308</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U184" t="inlineStr">
@@ -37201,11 +37201,11 @@
         <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>0.1894157761245646</v>
+        <v>0.1909971957049242</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">

--- a/diseases/d071/2010-2014.xlsx
+++ b/diseases/d071/2010-2014.xlsx
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">

--- a/diseases/d071/2010-2014.xlsx
+++ b/diseases/d071/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36248,7 +36248,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
